--- a/data/trans_orig/Q5404-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2007</t>
+          <t>Población según si es capaz de manejar dinero en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53430</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>23299</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80999</t>
+          <t>79526</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88597</t>
+          <t>88540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,62 +1224,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8572</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>8807</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -1302,97 +1302,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>41603</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57809</t>
+          <t>58044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60182</t>
+          <t>60334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>69118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23249</t>
+          <t>23239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78458</t>
+          <t>79578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90672</t>
+          <t>91347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28379</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233016</t>
+          <t>233466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>248492</t>
+          <t>248591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73558</t>
+          <t>73256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83508</t>
+          <t>83521</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>311612</t>
+          <t>312221</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>329995</t>
+          <t>329461</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>19273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>54476</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>70327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86723</t>
+          <t>86046</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121946</t>
+          <t>121841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138701</t>
+          <t>139253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>25353</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>377861</t>
+          <t>376814</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>400841</t>
+          <t>401158</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>380992</t>
+          <t>380802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>404324</t>
+          <t>406661</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18552</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>40464</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>28868</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53025</t>
+          <t>54918</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41945</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70846</t>
+          <t>69137</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>458474</t>
+          <t>457723</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>479319</t>
+          <t>479479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>597619</t>
+          <t>597520</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>627669</t>
+          <t>628825</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1063851</t>
+          <t>1065782</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1103495</t>
+          <t>1101469</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2012</t>
+          <t>Población según si es capaz de manejar dinero en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,97 +4159,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2151</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37348</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60693</t>
+          <t>60814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68223</t>
+          <t>68248</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59515</t>
+          <t>59522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>64593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77277</t>
+          <t>77286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,62 +5106,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>6569</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6717</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25286</t>
+          <t>24960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99282</t>
+          <t>99386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114388</t>
+          <t>114287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41849</t>
+          <t>42152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51568</t>
+          <t>52233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146528</t>
+          <t>146162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164352</t>
+          <t>163951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>19900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33036</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194092</t>
+          <t>194933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>214214</t>
+          <t>214866</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>44360</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55886</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>244221</t>
+          <t>244231</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>266514</t>
+          <t>267159</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12613</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29422</t>
+          <t>29468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>33730</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>17798</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37836</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85185</t>
+          <t>84542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97440</t>
+          <t>97365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>134398</t>
+          <t>133960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158091</t>
+          <t>157887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>224677</t>
+          <t>223896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251017</t>
+          <t>250360</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36495</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26926</t>
+          <t>27491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52176</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>315271</t>
+          <t>318496</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>346224</t>
+          <t>347180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318198</t>
+          <t>321332</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>348099</t>
+          <t>348797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61822</t>
+          <t>60761</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54947</t>
+          <t>54558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88460</t>
+          <t>87572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>44532</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60820</t>
+          <t>61068</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93462</t>
+          <t>94122</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>85954</t>
+          <t>85491</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>128306</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>488260</t>
+          <t>490400</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>519724</t>
+          <t>520596</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>595915</t>
+          <t>598062</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>638632</t>
+          <t>639701</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1099639</t>
+          <t>1098203</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1150246</t>
+          <t>1151290</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2016</t>
+          <t>Población según si es capaz de manejar dinero en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,97 +7585,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63518</t>
+          <t>63151</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94425</t>
+          <t>94361</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104188</t>
+          <t>104175</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,62 +8076,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4657</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5179</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45119</t>
+          <t>45716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52479</t>
+          <t>52471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60738</t>
+          <t>61006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69938</t>
+          <t>69999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,62 +8532,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108366</t>
+          <t>109101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117966</t>
+          <t>117807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151260</t>
+          <t>151671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162037</t>
+          <t>162472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>24056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187577</t>
+          <t>187052</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>198927</t>
+          <t>198940</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>77043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93561</t>
+          <t>94077</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>270915</t>
+          <t>272319</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>290064</t>
+          <t>290532</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>35525</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126330</t>
+          <t>126011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138259</t>
+          <t>138902</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126727</t>
+          <t>125556</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>145256</t>
+          <t>145097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259376</t>
+          <t>257581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>281583</t>
+          <t>280874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>33762</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>33762</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>361151</t>
+          <t>359182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387680</t>
+          <t>387725</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>361151</t>
+          <t>359182</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>387680</t>
+          <t>387725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45695</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27245</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55032</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>35217</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>65283</t>
+          <t>65570</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53360</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>87831</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>549089</t>
+          <t>549165</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>569142</t>
+          <t>568723</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>673432</t>
+          <t>674130</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>711998</t>
+          <t>712050</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1231819</t>
+          <t>1230986</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1275249</t>
+          <t>1275599</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2023</t>
+          <t>Población según si es capaz de manejar dinero en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,62 +11046,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103213</t>
+          <t>103176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107417</t>
+          <t>107415</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59492</t>
+          <t>59716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64306</t>
+          <t>64424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>164985</t>
+          <t>164616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171055</t>
+          <t>170988</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87755</t>
+          <t>87773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93958</t>
+          <t>93899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41213</t>
+          <t>41156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45767</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130701</t>
+          <t>131077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138604</t>
+          <t>138605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15316</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92123</t>
+          <t>92073</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99716</t>
+          <t>99851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49624</t>
+          <t>49651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138463</t>
+          <t>138617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148248</t>
+          <t>147918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24905</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>40769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>207640</t>
+          <t>207950</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222875</t>
+          <t>222062</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>294336</t>
+          <t>294001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>324050</t>
+          <t>324234</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>508961</t>
+          <t>509795</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>553388</t>
+          <t>552624</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>470</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80658</t>
+          <t>80606</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88603</t>
+          <t>88440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165043</t>
+          <t>165495</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179259</t>
+          <t>179497</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250339</t>
+          <t>249578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>266561</t>
+          <t>265893</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25654</t>
+          <t>26569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31637</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>31115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49087</t>
+          <t>48779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>251964</t>
+          <t>251953</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>273284</t>
+          <t>272291</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>254975</t>
+          <t>254996</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>276095</t>
+          <t>276209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>51190</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58925</t>
+          <t>59069</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40598</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38338</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97840</t>
+          <t>97825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>66068</t>
+          <t>69223</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>126546</t>
+          <t>126976</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>588517</t>
+          <t>588081</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>608297</t>
+          <t>608880</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>871444</t>
+          <t>873034</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>959521</t>
+          <t>959904</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1477523</t>
+          <t>1476548</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1562669</t>
+          <t>1556512</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5404-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53642</t>
+          <t>53663</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79526</t>
+          <t>80865</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88540</t>
+          <t>88582</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41603</t>
+          <t>42553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58044</t>
+          <t>59264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60334</t>
+          <t>60099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69118</t>
+          <t>69163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79578</t>
+          <t>79287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91347</t>
+          <t>91150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233466</t>
+          <t>234244</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>248591</t>
+          <t>249224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73256</t>
+          <t>72640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83521</t>
+          <t>83480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>312221</t>
+          <t>313499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>329461</t>
+          <t>330758</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19273</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>47273</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54476</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70327</t>
+          <t>70365</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86046</t>
+          <t>85906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121841</t>
+          <t>122081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139253</t>
+          <t>138920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25753</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>28373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28003</t>
+          <t>28802</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>376814</t>
+          <t>376957</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>401158</t>
+          <t>400423</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>380802</t>
+          <t>381237</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>406661</t>
+          <t>404677</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54918</t>
+          <t>54281</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>31688</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>46644</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>40452</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69137</t>
+          <t>69752</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>457723</t>
+          <t>458694</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>479479</t>
+          <t>479059</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>597520</t>
+          <t>598847</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>628825</t>
+          <t>628560</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1065782</t>
+          <t>1065500</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1101469</t>
+          <t>1103135</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>37465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60814</t>
+          <t>60962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68248</t>
+          <t>68252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59522</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64593</t>
+          <t>64651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77286</t>
+          <t>77298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99386</t>
+          <t>98469</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114287</t>
+          <t>114370</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42152</t>
+          <t>41815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52233</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146162</t>
+          <t>145785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163951</t>
+          <t>164697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24324</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>35090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194933</t>
+          <t>194800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>214866</t>
+          <t>214623</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44360</t>
+          <t>44628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>55996</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>244231</t>
+          <t>244493</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>267159</t>
+          <t>268400</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>36427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33730</t>
+          <t>33782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39265</t>
+          <t>38761</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84542</t>
+          <t>84782</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97365</t>
+          <t>97573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>133960</t>
+          <t>132627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157887</t>
+          <t>156608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>223896</t>
+          <t>225477</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>250360</t>
+          <t>252685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35395</t>
+          <t>35559</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>51441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27491</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>50647</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>318496</t>
+          <t>316098</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>347180</t>
+          <t>345659</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>321332</t>
+          <t>317662</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>348797</t>
+          <t>348400</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33968</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60761</t>
+          <t>60006</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54558</t>
+          <t>52869</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87572</t>
+          <t>87470</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>61068</t>
+          <t>59973</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>94122</t>
+          <t>95577</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>85491</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>126044</t>
+          <t>127705</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>490400</t>
+          <t>488971</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>520596</t>
+          <t>520483</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>598062</t>
+          <t>597944</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>639701</t>
+          <t>640974</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1098203</t>
+          <t>1101404</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1151290</t>
+          <t>1151487</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63151</t>
+          <t>63655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94361</t>
+          <t>94794</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104175</t>
+          <t>104198</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45716</t>
+          <t>45576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52471</t>
+          <t>52453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61006</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69999</t>
+          <t>69934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,82 +8625,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2458</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7435</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>16,09%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>7706</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>14569</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>8,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2458</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7598</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>7706</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3221</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>14283</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109101</t>
+          <t>108052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117807</t>
+          <t>117479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>38774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151671</t>
+          <t>151598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162472</t>
+          <t>162498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24056</t>
+          <t>25461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187052</t>
+          <t>188171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>198940</t>
+          <t>198961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77043</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94077</t>
+          <t>93660</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>272319</t>
+          <t>269765</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>290532</t>
+          <t>290201</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12343</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>26444</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126011</t>
+          <t>126981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138902</t>
+          <t>138961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125556</t>
+          <t>127317</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>145097</t>
+          <t>146108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257581</t>
+          <t>258993</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>280874</t>
+          <t>281608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>32946</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>32946</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>26234</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>26234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>359182</t>
+          <t>361981</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387725</t>
+          <t>388068</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>359182</t>
+          <t>361981</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>387725</t>
+          <t>388068</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>42416</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>25990</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>54416</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>31637</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>65570</t>
+          <t>64914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54446</t>
+          <t>52818</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>89845</t>
+          <t>86129</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>549165</t>
+          <t>548007</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>568723</t>
+          <t>568650</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>674130</t>
+          <t>675486</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>712050</t>
+          <t>713377</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1230986</t>
+          <t>1233252</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1275599</t>
+          <t>1274705</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -11086,12 +11086,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,67 +11154,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>4118</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>8157</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>4,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>3527</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1375</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>7149</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106155</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103176</t>
+          <t>115322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107415</t>
+          <t>119827</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62590</t>
+          <t>71643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59716</t>
+          <t>68358</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64424</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>168746</t>
+          <t>190230</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>164616</t>
+          <t>186110</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>170988</t>
+          <t>192674</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91633</t>
+          <t>101422</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87773</t>
+          <t>97220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93899</t>
+          <t>103449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44057</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41156</t>
+          <t>47185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>53672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135690</t>
+          <t>152675</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131077</t>
+          <t>147366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138605</t>
+          <t>156045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>429</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -11963,12 +11963,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>907</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96941</t>
+          <t>107187</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92073</t>
+          <t>102164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99851</t>
+          <t>109943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>51839</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49651</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>144044</t>
+          <t>159027</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138617</t>
+          <t>152729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147918</t>
+          <t>162891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16932</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25629</t>
+          <t>26670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40769</t>
+          <t>34497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>216525</t>
+          <t>237025</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>207950</t>
+          <t>227836</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222062</t>
+          <t>244093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>315616</t>
+          <t>118984</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>294001</t>
+          <t>113068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>324234</t>
+          <t>123180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>532141</t>
+          <t>356009</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>509795</t>
+          <t>346783</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>552624</t>
+          <t>364380</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>25059</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>33009</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>85654</t>
+          <t>94027</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80606</t>
+          <t>88212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88440</t>
+          <t>97242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>173325</t>
+          <t>186437</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165495</t>
+          <t>177857</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179497</t>
+          <t>193712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>258979</t>
+          <t>280464</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>249578</t>
+          <t>270971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265893</t>
+          <t>288936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26569</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>14013</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>28628</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>516</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>39440</t>
+          <t>42235</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48729</t>
+          <t>52105</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>42751</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31115</t>
+          <t>34347</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>52646</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -13512,27 +13512,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>263056</t>
+          <t>282324</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>251953</t>
+          <t>270510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>272291</t>
+          <t>292831</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>265728</t>
+          <t>285084</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>254996</t>
+          <t>272954</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>276209</t>
+          <t>295068</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>345137</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324284</t>
+          <t>348413</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51190</t>
+          <t>52939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>45691</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>59069</t>
+          <t>60159</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>32786</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41075</t>
+          <t>44169</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>80712</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>67681</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97825</t>
+          <t>93374</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>104981</t>
+          <t>113498</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>69223</t>
+          <t>98810</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>126976</t>
+          <t>130641</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>599580</t>
+          <t>661010</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>588081</t>
+          <t>648364</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>608880</t>
+          <t>670212</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>905747</t>
+          <t>762479</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>873034</t>
+          <t>746818</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>959904</t>
+          <t>778358</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1505327</t>
+          <t>1423488</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1476548</t>
+          <t>1403918</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1556512</t>
+          <t>1441331</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>884175</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>884175</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>884175</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1655999</t>
+          <t>1585838</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1655999</t>
+          <t>1585838</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1655999</t>
+          <t>1585838</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
